--- a/BILL 301 TO.xlsx
+++ b/BILL 301 TO.xlsx
@@ -54,19 +54,19 @@
     <t>TAX INVOICE</t>
   </si>
   <si>
-    <t>SAASTHA ENGINEERING WORKS</t>
+    <t>EXAMPLE ENGINEERING WORKS</t>
   </si>
   <si>
     <t>Manufacturing Traders of Machinery,Precision Job Works &amp; Industrial Products</t>
   </si>
   <si>
-    <t>GST No.27AAMPE1857D2ZT  MSME NO.UDYAM-MH-33-0054711</t>
+    <t>GST No.27AAAPE1234F1Z9  MSME NO.UDYAM-MH-00-0000001</t>
   </si>
   <si>
-    <t>Office Address: Unit No.1,GalaNo.2 &amp; 3,NearITI Circle,Road No.28,Kailash Nagar,Wagle Estate,Thane - 400 604,State- Maharashtra</t>
+    <t>Office Address: Unit No.1,GalaNo.2 &amp; 3,NearExample Circle,Road No.28,Example Nagar,Example Estate,Example City - 000 001,State- Maharashtra</t>
   </si>
   <si>
-    <t>Email (1):saastha01@gmail.com Email(2): saasthaenggworks2011@gmail.com Mob.9969434432 &amp; 9969142688</t>
+    <t>Email (1):example1@example.com Email(2): example2@example.com Mob.9000000001 &amp; 9000000002</t>
   </si>
   <si>
     <t>Details of Receipient (Billed To)</t>
@@ -75,13 +75,13 @@
     <t>Original Copy of Invoice for Receipt                                            Duplicate &amp; Triplicate Supplier or Transporter</t>
   </si>
   <si>
-    <t>M/s. Hawkins Cookers Ltd.,</t>
+    <t>M/s. Example Cookers Ltd.,</t>
   </si>
   <si>
     <t>INVOICE NO.:</t>
   </si>
   <si>
-    <t>SEW/301/2026-27</t>
+    <t>FIX/301/2026-27</t>
   </si>
   <si>
     <t xml:space="preserve">Date: </t>
@@ -93,19 +93,19 @@
     <t>Our Challan No.:</t>
   </si>
   <si>
-    <t>Wagle Industrial Estate,</t>
+    <t>Example Industrial Estate,</t>
   </si>
   <si>
     <t>Your Challan No.:</t>
   </si>
   <si>
-    <t>Thane - 400 604.</t>
+    <t>Example City - 000 001.</t>
   </si>
   <si>
     <t>Purchase Order No.:</t>
   </si>
   <si>
-    <t>WT/PO/TRM/600317</t>
+    <t>WT/PO/TRM/9000001</t>
   </si>
   <si>
     <t xml:space="preserve">                                                                          </t>
@@ -120,13 +120,13 @@
     <t>PLACE OF SUPPLY</t>
   </si>
   <si>
-    <t xml:space="preserve">THANE                          </t>
+    <t xml:space="preserve">EXAMPLE CITY                   </t>
   </si>
   <si>
     <t>STATE CODE:27</t>
   </si>
   <si>
-    <t>Party's GST No.27AAACH1784M1Z9</t>
+    <t>Party's GST No.27AAACD5678E1Z9</t>
   </si>
   <si>
     <t>Transporter Mode</t>
@@ -189,13 +189,13 @@
     <t>ADD:  CGST</t>
   </si>
   <si>
-    <t>Bank Name: THE FEDERAL BANK LTD</t>
+    <t>Bank Name: EXAMPLE BANK LTD</t>
   </si>
   <si>
     <t>ADD:  SGST</t>
   </si>
   <si>
-    <t>ACCOUNT NUMBER:17750200004019</t>
+    <t>ACCOUNT NUMBER:00000000123456</t>
   </si>
   <si>
     <t>ADD:  IGST</t>
@@ -204,13 +204,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>BRANCH: LOUISWADI THANE</t>
+    <t>BRANCH: EXAMPLE BRANCH</t>
   </si>
   <si>
     <t>Total Amount :GST</t>
   </si>
   <si>
-    <t>IFSC CODE:FDRL0001775</t>
+    <t>IFSC CODE:EXAM0000001</t>
   </si>
   <si>
     <t>Total Amount After Tax</t>
@@ -234,7 +234,7 @@
     <t>Terms &amp; Conditions:</t>
   </si>
   <si>
-    <t>For SAASTHA ENGINEERING WORKS</t>
+    <t>For EXAMPLE ENGINEERING WORKS</t>
   </si>
   <si>
     <t>1.Payment requested within 15 DAYS</t>
@@ -258,10 +258,10 @@
     <t>TRIPLICATE</t>
   </si>
   <si>
-    <t>SEW/302/2026-27</t>
+    <t>FIX/302/2026-27</t>
   </si>
   <si>
-    <t>WT/PO/CP/600782</t>
+    <t>WT/PO/CP/9000002</t>
   </si>
   <si>
     <t>1.5L IC CONTURA BODY DRAW CUM STR CIRCLE LOCATOR</t>
@@ -279,10 +279,10 @@
     <t>Total Invoice Amount in Words:  NINETEEN THOUSAND AND EIGHT HUNDRED ONLY</t>
   </si>
   <si>
-    <t>SEW/303/2026-27</t>
+    <t>FIX/303/2026-27</t>
   </si>
   <si>
-    <t xml:space="preserve">WT/PO/TRM/600312 </t>
+    <t xml:space="preserve">WT/PO/TRM/9000002 </t>
   </si>
   <si>
     <t>1.2L STEAM KETTLE BODY TOP CURLING TOOL BASE PLATE</t>
@@ -294,10 +294,10 @@
     <t>Total Invoice Amount in Words:  TWENTY FIVE THOUSAND NINE  HUNDRED AND SEVENTY TWO ONLY</t>
   </si>
   <si>
-    <t>SEW/304/2026-27</t>
+    <t>FIX/304/2026-27</t>
   </si>
   <si>
-    <t xml:space="preserve">WT/PO/TRM/600307 </t>
+    <t xml:space="preserve">WT/PO/TRM/9000003 </t>
   </si>
   <si>
     <t xml:space="preserve">QUIK SS CW BODY TO BRACKET PW TOP ELECTRODE </t>
@@ -309,10 +309,10 @@
     <t>Total Invoice Amount in Words:  THIRTY FOUR THOUSAND NINE HUNDRED AND TWENTY EIGHT ONLY</t>
   </si>
   <si>
-    <t>SEW/305/2026-27</t>
+    <t>FIX/305/2026-27</t>
   </si>
   <si>
-    <t>WT/PO/CP/600784</t>
+    <t>WT/PO/CP/9000003</t>
   </si>
   <si>
     <t>2222 9329 6081</t>
@@ -357,16 +357,16 @@
     <t>Total Invoice Amount in Words:  THREE LAKH NINETY NINE THOUSAND NINE  HUNDRED AND NINETY ONE ONLY</t>
   </si>
   <si>
-    <t>SEW/306/2026-27</t>
+    <t>FIX/306/2026-27</t>
   </si>
   <si>
-    <t>WT/PO/CP/600785</t>
+    <t>WT/PO/CP/9000004</t>
   </si>
   <si>
     <t>2622 9330 5558</t>
   </si>
   <si>
-    <t>MH 04 JQ 4172</t>
+    <t>MH 00 EX 0000</t>
   </si>
   <si>
     <t>1.4L KETTLE LID CUP DRAW PRESSURE PLATE ASSY</t>
@@ -414,10 +414,10 @@
     <t>Total Invoice Amount in Words:  TWO LAKH FORTY THREE THOUSAND SEVEN HUNDRED AND SIXTY FOUR ONLY</t>
   </si>
   <si>
-    <t>SEW/307/2026-27</t>
+    <t>FIX/307/2026-27</t>
   </si>
   <si>
-    <t>WT/PO/TRM/600320</t>
+    <t>WT/PO/TRM/9000004</t>
   </si>
   <si>
     <t>STD QUIK SS COOKER BODY SPINNING LIPPING MANDREL</t>
@@ -429,10 +429,10 @@
     <t>Total Invoice Amount in Words:  THIRTY FIVE THOUSAND AND FOUR HUNDRED ONLY</t>
   </si>
   <si>
-    <t>SEW/308/2026-27</t>
+    <t>FIX/308/2026-27</t>
   </si>
   <si>
-    <t xml:space="preserve">WT/PO/CP/600779  </t>
+    <t xml:space="preserve">WT/PO/CP/9000005  </t>
   </si>
   <si>
     <t xml:space="preserve">280T INCREDIBLE MACHINE ADAPTOR 390 Lg  </t>
@@ -444,7 +444,7 @@
     <t>Total Invoice Amount in Words:  TWENTY NINE THOUSAND ONE HUNDRED AND SEVENTY ONLY</t>
   </si>
   <si>
-    <t>SEW/309/2026-27</t>
+    <t>FIX/309/2026-27</t>
   </si>
   <si>
     <t xml:space="preserve">1.4L KETTLE LID RIM ID FLANGE TRIMMING MANDREL </t>
@@ -456,10 +456,10 @@
     <t>Total Invoice Amount in Words:  EIGHTEEN THOUSAND FIVE HUNDRED AND TWENTY SIX ONLY</t>
   </si>
   <si>
-    <t>SEW/310/2026-27</t>
+    <t>FIX/310/2026-27</t>
   </si>
   <si>
-    <t>WT/PO/CP/600786</t>
+    <t>WT/PO/CP/9000006</t>
   </si>
   <si>
     <t>2622 9407 9706</t>
@@ -498,16 +498,16 @@
     <t>Total Invoice Amount in Words:  THREE LAKH THIRTY THOUSAND EIGHT HUNDRED AND SIXTYSIX ONLY</t>
   </si>
   <si>
-    <t>SEW/311/2026-27</t>
+    <t>FIX/311/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/260361</t>
+    <t>WT/OGC/TR/9000001</t>
   </si>
   <si>
     <t>Service Order No.:</t>
   </si>
   <si>
-    <t>WT/SO/2602597</t>
+    <t>WT/SO/9000002</t>
   </si>
   <si>
     <t xml:space="preserve">                                         </t>
@@ -531,13 +531,13 @@
     <t>1.Payment requested within 40 DAYS</t>
   </si>
   <si>
-    <t>SEW/312/2026-27</t>
+    <t>FIX/312/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/260900</t>
+    <t>WT/OGC/TR/9000002</t>
   </si>
   <si>
-    <t>WT/SO/2602132</t>
+    <t>WT/SO/9000003</t>
   </si>
   <si>
     <t>IC PLATE COMBINE FITTING TOOL BOTTOM PUNCH HOLDER</t>
@@ -549,13 +549,13 @@
     <t>Total Invoice Amount in Words:- SIX THOUSAND TWO HUNDRED AND EIGHTY SEVEN ONLY</t>
   </si>
   <si>
-    <t>SEW/313/2026-27</t>
+    <t>FIX/313/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/261166</t>
+    <t>WT/OGC/TR/9000003</t>
   </si>
   <si>
-    <t>WT/SO/2602876</t>
+    <t>WT/SO/9000004</t>
   </si>
   <si>
     <t>QSF22 BODY BOTTOM FLATTENING CUM DISHING TOOL-</t>
@@ -567,13 +567,13 @@
     <t>Total Invoice Amount in Words:- FIVE THOUSAND AND NINE HUNDRED ONLY</t>
   </si>
   <si>
-    <t>SEW/314/2026-27</t>
+    <t>FIX/314/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/261194</t>
+    <t>WT/OGC/TR/9000004</t>
   </si>
   <si>
-    <t>WT/SO/2602878</t>
+    <t>WT/SO/9000005</t>
   </si>
   <si>
     <t>5L TP CL COOKER BODY SPINNING LIPPING MANDREL-MAIN</t>
@@ -585,13 +585,13 @@
     <t>Total Invoice Amount in Words:- SEVEN THOUSAND SIX HUNDRED AND SEVENTY ONLY</t>
   </si>
   <si>
-    <t>SEW/315/2026-27</t>
+    <t>FIX/315/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/261177</t>
+    <t>WT/OGC/TR/9000005</t>
   </si>
   <si>
-    <t>WT/SO/2602891</t>
+    <t>WT/SO/9000006</t>
   </si>
   <si>
     <t xml:space="preserve">TP COOKER BODY AUTO TRIMMING CUTTER FOR REDSON </t>
@@ -603,13 +603,13 @@
     <t>Total Invoice Amount in Words:- FOUR THOUSAND SEVEN HUNDRED AND TWENTY ONLY</t>
   </si>
   <si>
-    <t>SEW/316/2026-27</t>
+    <t>FIX/316/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/261186</t>
+    <t>WT/OGC/TR/9000006</t>
   </si>
   <si>
-    <t>WT/SO/2602877</t>
+    <t>WT/SO/9000007</t>
   </si>
   <si>
     <t>5L TP PRO DEEP KADHAI BODY FLANGE FLATTENING TOOL-</t>
@@ -621,13 +621,13 @@
     <t>Total Invoice Amount in Words:- EIGHTY  THOUSAND EIGHT HUNDRED AND FIFTY ONLY</t>
   </si>
   <si>
-    <t>SEW/317/2026-27</t>
+    <t>FIX/317/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/261199</t>
+    <t>WT/OGC/TR/9000007</t>
   </si>
   <si>
-    <t>WT/SO/2602879</t>
+    <t>WT/SO/9000008</t>
   </si>
   <si>
     <t>STD SS BODY BOTTOM FLATTENING TOOL-TOOL FOR HARD</t>
@@ -639,22 +639,22 @@
     <t>Total Invoice Amount in Words:- TEN  THOUSAND SIX HUNDRED AND TWENTY ONLY</t>
   </si>
   <si>
-    <t>SEW/318/2026-27</t>
+    <t>FIX/318/2026-27</t>
   </si>
   <si>
-    <t>WT/OGC/TR/260899</t>
+    <t>WT/OGC/TR/9000008</t>
   </si>
   <si>
-    <t>WT/SO/2602875</t>
+    <t>WT/SO/9000009</t>
   </si>
   <si>
     <t>JB</t>
   </si>
   <si>
-    <t>SEW/319/2026-27</t>
+    <t>FIX/319/2026-27</t>
   </si>
   <si>
-    <t>WT/PO/TRM/600323</t>
+    <t>WT/PO/TRM/9000005</t>
   </si>
   <si>
     <t>IS SS LID VTH &amp; SVH HOLE PIERCING TOOL LOCATING PIN</t>
@@ -666,7 +666,7 @@
     <t>Total Invoice Amount in Words:  FOUR THOUSAND SEVEN HUNDRED AND TWENTY ONLY</t>
   </si>
   <si>
-    <t>SEW/320/2026-27</t>
+    <t>FIX/320/2026-27</t>
   </si>
   <si>
     <t>abc</t>
@@ -675,7 +675,7 @@
     <t>29/09/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">WT/PO/CP/600799 </t>
+    <t xml:space="preserve">WT/PO/CP/9000007 </t>
   </si>
   <si>
     <t xml:space="preserve">MAIN ROLLER HARD FOR RIGHT ANGLE MACHINE DIA </t>

--- a/BILL 301 TO.xlsx
+++ b/BILL 301 TO.xlsx
@@ -315,7 +315,7 @@
     <t>WT/PO/CP/9000003</t>
   </si>
   <si>
-    <t>2222 9329 6081</t>
+    <t>9999 9000 0001</t>
   </si>
   <si>
     <t>1.2L STEAM KETTLE BODYCUM FLANGE FORMING TOOL</t>
@@ -363,7 +363,7 @@
     <t>WT/PO/CP/9000004</t>
   </si>
   <si>
-    <t>2622 9330 5558</t>
+    <t>9999 9000 0002</t>
   </si>
   <si>
     <t>MH 00 EX 0000</t>
@@ -462,7 +462,7 @@
     <t>WT/PO/CP/9000006</t>
   </si>
   <si>
-    <t>2622 9407 9706</t>
+    <t>9999 9000 0003</t>
   </si>
   <si>
     <t>3.5L NS TP DK BODY MASKING FIXTURE FOR INSIDE SAND BLASTING (3010273-29376,29377,29378,29379)</t>
